--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ5"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1173,6 +1173,108 @@
       <c r="AZ5" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/105419785</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>136414686</v>
+      </c>
+      <c r="B6" t="n">
+        <v>111407</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219677</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Murgröna</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hedera helix</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Domderörsbackarna, Domderörsbackarna, Öl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>597971</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6275212</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Mörbylånga</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Öland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Gårdby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136414686</t>
         </is>
       </c>
     </row>
@@ -1182,6 +1284,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111407</v>
+        <v>111408</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111408</v>
+        <v>111421</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 34431-2026 artfynd.xlsx
+++ b/artfynd/A 34431-2026 artfynd.xlsx
@@ -1181,7 +1181,7 @@
         <v>136414686</v>
       </c>
       <c r="B6" t="n">
-        <v>111421</v>
+        <v>111422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
